--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.061532778910677</v>
+        <v>1.147499076572985</v>
       </c>
       <c r="D2" t="n">
-        <v>5.859326328072666</v>
+        <v>0.9521405283118083</v>
       </c>
       <c r="E2" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F2" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.01962069183215</v>
+        <v>2.115688362422724</v>
       </c>
       <c r="D3" t="n">
-        <v>12.62513112070789</v>
+        <v>2.051583807115032</v>
       </c>
       <c r="E3" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F3" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.447046292317367</v>
+        <v>0.8851450225015721</v>
       </c>
       <c r="D4" t="n">
-        <v>5.399466698252357</v>
+        <v>0.877413338466008</v>
       </c>
       <c r="E4" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F4" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.19054146619327</v>
+        <v>3.443462988256407</v>
       </c>
       <c r="D5" t="n">
-        <v>21.28832950293323</v>
+        <v>3.45935354422665</v>
       </c>
       <c r="E5" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F5" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.82124218723004</v>
+        <v>5.008451855424882</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10466322713359</v>
+        <v>2.617007774409208</v>
       </c>
       <c r="E6" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F6" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.66088879253707</v>
+        <v>5.632394428787273</v>
       </c>
       <c r="D7" t="n">
-        <v>8.191543471196651</v>
+        <v>1.331125814069456</v>
       </c>
       <c r="E7" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F7" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.71358925622369</v>
+        <v>2.22845825413635</v>
       </c>
       <c r="D8" t="n">
-        <v>7.279128347233875</v>
+        <v>1.182858356425505</v>
       </c>
       <c r="E8" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F8" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.8152095211635</v>
+        <v>4.68247154718907</v>
       </c>
       <c r="D9" t="n">
-        <v>26.16588136186235</v>
+        <v>4.251955721302632</v>
       </c>
       <c r="E9" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F9" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.846352587820588</v>
+        <v>0.7875322955208456</v>
       </c>
       <c r="D10" t="n">
-        <v>9.708362218895008</v>
+        <v>1.577608860570439</v>
       </c>
       <c r="E10" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F10" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.02798670750424</v>
+        <v>2.442047839969439</v>
       </c>
       <c r="D11" t="n">
-        <v>7.601271341816727</v>
+        <v>1.235206593045218</v>
       </c>
       <c r="E11" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F11" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.78766458048727</v>
+        <v>4.352995494329182</v>
       </c>
       <c r="D12" t="n">
-        <v>14.45621927200398</v>
+        <v>2.349135631700646</v>
       </c>
       <c r="E12" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F12" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.05146118505596</v>
+        <v>4.558362442571593</v>
       </c>
       <c r="D13" t="n">
-        <v>25.94259718653013</v>
+        <v>4.215672042811147</v>
       </c>
       <c r="E13" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F13" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.04405225593701</v>
+        <v>5.857158491589765</v>
       </c>
       <c r="D14" t="n">
-        <v>37.45694014517196</v>
+        <v>6.086752773590443</v>
       </c>
       <c r="E14" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F14" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.9462132015426</v>
+        <v>6.816259645250672</v>
       </c>
       <c r="D15" t="n">
-        <v>42.1981725869236</v>
+        <v>6.857203045375085</v>
       </c>
       <c r="E15" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F15" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>49.43243212518941</v>
+        <v>8.032770220343281</v>
       </c>
       <c r="D16" t="n">
-        <v>44.55140921347051</v>
+        <v>7.239603997188959</v>
       </c>
       <c r="E16" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F16" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>46.25259402988987</v>
+        <v>7.516046529857104</v>
       </c>
       <c r="D17" t="n">
-        <v>30.23911121976553</v>
+        <v>4.913855573211899</v>
       </c>
       <c r="E17" t="n">
-        <v>13.93417167099207</v>
+        <v>2.264302896536212</v>
       </c>
       <c r="F17" t="n">
-        <v>12.87663356577528</v>
+        <v>2.092452954438483</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
